--- a/data/trans_bre/PCS12_SP_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 20,68</t>
+          <t>3,91; 19,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 12,99</t>
+          <t>-4,54; 12,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 17,25</t>
+          <t>0,48; 17,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 27,94</t>
+          <t>10,54; 27,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 51,36</t>
+          <t>7,92; 49,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 28,2</t>
+          <t>-8,23; 27,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 42,02</t>
+          <t>1,06; 41,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 52,31</t>
+          <t>15,64; 50,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,31</t>
+          <t>3,86; 16,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,2</t>
+          <t>6,93; 19,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 14,68</t>
+          <t>1,95; 13,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 17,45</t>
+          <t>4,05; 17,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 35,66</t>
+          <t>7,22; 36,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 40,77</t>
+          <t>12,66; 41,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 34,76</t>
+          <t>4,56; 33,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 43,73</t>
+          <t>8,1; 42,68</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,83; 34,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 18,46</t>
+          <t>3,36; 18,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 10,38</t>
+          <t>-3,11; 11,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 6,32</t>
+          <t>-7,88; 7,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,16; 91,36</t>
+          <t>43,49; 94,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 47,93</t>
+          <t>7,41; 49,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 38,69</t>
+          <t>-9,27; 44,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 13,06</t>
+          <t>-14,01; 14,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 26,64</t>
+          <t>12,75; 26,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 20,5</t>
+          <t>5,5; 20,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 15,48</t>
+          <t>0,58; 15,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 5,95</t>
+          <t>-25,99; 6,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,35; 71,18</t>
+          <t>28,18; 72,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 61,85</t>
+          <t>14,05; 60,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 30,39</t>
+          <t>1,08; 30,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 11,7</t>
+          <t>-50,38; 12,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 24,59</t>
+          <t>5,26; 24,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 23,11</t>
+          <t>3,36; 23,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,45</t>
+          <t>-1,53; 16,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 18,75</t>
+          <t>2,9; 19,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 85,42</t>
+          <t>12,63; 84,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 60,26</t>
+          <t>6,23; 59,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 62,08</t>
+          <t>-5,14; 65,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 50,85</t>
+          <t>6,11; 52,1</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,29; 33,06</t>
+          <t>16,48; 32,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 16,86</t>
+          <t>-0,01; 17,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 18,42</t>
+          <t>0,99; 18,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 14,7</t>
+          <t>-0,12; 15,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,84; 85,98</t>
+          <t>34,62; 87,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 40,82</t>
+          <t>0,9; 42,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 61,25</t>
+          <t>2,59; 59,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 29,09</t>
+          <t>-0,2; 31,54</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 17,6</t>
+          <t>5,8; 17,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 16,74</t>
+          <t>6,34; 16,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 16,41</t>
+          <t>4,88; 16,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 36,86</t>
+          <t>1,9; 36,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 43,57</t>
+          <t>12,63; 40,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,6; 43,39</t>
+          <t>14,12; 44,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 46,49</t>
+          <t>11,11; 46,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 81,81</t>
+          <t>3,93; 85,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,68</t>
+          <t>3,91; 13,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 13,2</t>
+          <t>3,08; 13,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,21</t>
+          <t>5,28; 15,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 11,18</t>
+          <t>-36,43; 10,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 38,22</t>
+          <t>9,54; 39,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,29; 33,88</t>
+          <t>6,87; 34,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,91; 51,62</t>
+          <t>15,1; 51,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 36,62</t>
+          <t>-48,11; 35,23</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,81</t>
+          <t>11,92; 16,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,92</t>
+          <t>7,89; 12,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,13</t>
+          <t>6,49; 11,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 12,41</t>
+          <t>-5,72; 12,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,35; 40,73</t>
+          <t>27,33; 41,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,15; 30,35</t>
+          <t>17,5; 30,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,5</t>
+          <t>16,09; 29,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 25,91</t>
+          <t>-11,39; 26,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,03</t>
+          <t>15,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 19,75</t>
+          <t>3,1; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 12,71</t>
+          <t>-3,72; 13,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 17,06</t>
+          <t>0,11; 17,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 27,68</t>
+          <t>7,76; 22,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 49,2</t>
+          <t>5,87; 51,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 27,7</t>
+          <t>-6,53; 32,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 41,22</t>
+          <t>-0,27; 40,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 50,91</t>
+          <t>11,53; 38,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,08</t>
+          <t>10,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 16,56</t>
+          <t>3,75; 16,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 19,38</t>
+          <t>6,85; 19,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 13,83</t>
+          <t>1,71; 14,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 17,29</t>
+          <t>3,82; 17,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 36,2</t>
+          <t>7,09; 36,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 41,59</t>
+          <t>12,76; 41,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 33,46</t>
+          <t>3,88; 34,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 42,68</t>
+          <t>7,92; 43,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,01%</t>
+          <t>-1,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,83; 34,72</t>
+          <t>19,68; 34,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,34</t>
+          <t>2,63; 17,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 11,49</t>
+          <t>-3,28; 11,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 7,01</t>
+          <t>-8,16; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,49; 94,38</t>
+          <t>43,06; 94,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 49,5</t>
+          <t>5,73; 45,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 44,72</t>
+          <t>-10,08; 40,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 14,36</t>
+          <t>-14,19; 12,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-14,05%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 26,61</t>
+          <t>12,33; 26,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 20,36</t>
+          <t>5,72; 20,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 15,51</t>
+          <t>0,69; 14,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 6,03</t>
+          <t>-1,11; 15,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,18; 72,34</t>
+          <t>27,57; 73,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 60,75</t>
+          <t>13,62; 60,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 30,3</t>
+          <t>1,12; 27,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 12,16</t>
+          <t>-2,08; 38,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 24,88</t>
+          <t>5,17; 24,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 23,23</t>
+          <t>4,37; 22,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 16,96</t>
+          <t>-1,31; 16,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 19,37</t>
+          <t>3,13; 18,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,63; 84,79</t>
+          <t>13,48; 83,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 59,94</t>
+          <t>8,57; 56,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 65,23</t>
+          <t>-4,7; 64,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 52,1</t>
+          <t>6,88; 51,18</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,48; 32,82</t>
+          <t>17,72; 33,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 17,48</t>
+          <t>0,41; 17,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 18,09</t>
+          <t>2,21; 18,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 15,57</t>
+          <t>0,07; 15,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,62; 87,14</t>
+          <t>37,43; 87,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 42,65</t>
+          <t>0,85; 40,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 59,94</t>
+          <t>5,67; 57,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 31,54</t>
+          <t>0,33; 30,83</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 17,1</t>
+          <t>5,49; 16,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 16,96</t>
+          <t>5,59; 17,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 16,34</t>
+          <t>5,59; 16,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 36,85</t>
+          <t>-2,97; 8,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 40,75</t>
+          <t>11,28; 39,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,12; 44,09</t>
+          <t>12,22; 44,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 46,58</t>
+          <t>13,41; 46,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 85,55</t>
+          <t>-5,52; 19,04</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-17,28%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,99</t>
+          <t>3,7; 14,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,51</t>
+          <t>3,01; 13,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,04</t>
+          <t>5,8; 15,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 10,78</t>
+          <t>4,22; 13,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,54; 39,5</t>
+          <t>8,89; 39,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 34,81</t>
+          <t>6,44; 34,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,1; 51,28</t>
+          <t>16,67; 52,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 35,23</t>
+          <t>13,29; 48,1</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,96</t>
+          <t>12,04; 16,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,75</t>
+          <t>7,93; 12,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,25</t>
+          <t>6,31; 11,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 12,23</t>
+          <t>5,03; 10,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,33; 41,75</t>
+          <t>27,23; 41,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,5; 30,03</t>
+          <t>17,39; 29,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,09; 29,91</t>
+          <t>15,74; 29,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 26,23</t>
+          <t>10,88; 22,7</t>
         </is>
       </c>
     </row>
